--- a/pacjenci/MATEUSZ JANIK.xlsx
+++ b/pacjenci/MATEUSZ JANIK.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -529,7 +529,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,7 +573,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,12 +617,12 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -674,17 +674,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -718,17 +718,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/MATEUSZ JANIK.xlsx
+++ b/pacjenci/MATEUSZ JANIK.xlsx
@@ -413,323 +413,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.04.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>HL, ocena przed leczeniem. Nie dostarczono do wglądu poprzednich wyników badań obrazowych.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 58 min od podania 18F-FDG. Glikemia: 117mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie liczne powiększone węzły chłonne szyjne : - przestrzeni przygardłowej obustronnie - po prawej śr. do 16 mm, spakietowane, SUVmax do 8,7, po lewej wym. do 14 x 20 mm, SUVmax do 10,4; - grup Ib - po prawej pojedyncze, graniczne, wym. do 11 x 8 mm, SUVmax 3,6; po lewej kilka częściowo spakietowanych wym. do 15 x 23 mm, SUVmax do 9,9; - grup II - po prawej mniej liczne, częściowo spakietowane w tym z grupą V po tej stronie, na przekrojach poprzecznych wym. do 26 x 16 mm (wg PET), SUVmax do 9,4; po lewej liczniejsze, spakietowane w ciągłości z grupą V po tej stronie, wym. do 37 x 48 mm, SUVmax do 10,6; - grup III-IV - po prawej liczniejsze, spakietowane, w ciągłości z pakietami węzłów nad- i podobojczykowych po tej stronie; największe pakiety na przekroju poprzecznym wym. do 36 x 30 mm, SUVmax do 11,4; po lewej mniej liczne, częściowo spakietowane, w ciągłości z pakietami nadobojczykowymi po tej stronie, wym. do 24 x 36 mm, SUVmax do 6,6;  - grup V - po prawej bardzo liczne spakietowane ciągnące się przez całą grupę, w największym wymiarze na przekroju poprzecznym ok. 39 x 50 mm, SUVmax do 12,3; po lewej nieco mniej liczne, częściowo spakietowane - największe wym. do 24 x 20 mm, SUVmax do 7,2. Aktywność metaboliczna w strukturach pierścienia chłonnego gardła, szczególnie wydatna w obrębie migdałków podniebiennych - obustronnie w przeglądowym TK wydają się być powiększone wym. do 15,9 mm (wg PET), SUVmax do 4,0.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyczne i spakietowane w grupach: - nad- i podobojczykowych oraz śródpiersia górnego w tym przymostkowe  po prawej w łączności z grupą IV szyjną, wym. do 40 x 19 mm, SUVmax do 7,1;  - nad- i podobojczykowych oraz śródpiersia górnego w tym przymostkowe po lewej w łączności z grupami węzłów przynaczyniowych i okna aortalno-płucnego, największy pakiet wym. do 56 x 38 mm, SUVmax do 10,8; - przytchawiczych górnych oraz dolnych - po prawej wielkości do 34 x 22 mm, SUVmax do 8,6; po lewej nieliczne wym. do 17 x 10 mm, SUVmax do 4,0; - podostrogowej i wnękowej po stronie prawej - wym. do 27 x 20 mm, SUVmax do 7,3; - wnękowej i oskrzelowo-płucnej po stronie lewej -  wym. do 23 x 17 mm wg PET, SUVmax do 11,2; - przedsercowej - w zachyłku przeponowo-sercowym tuż nad przeponą, poniżej koniuszka serca i w przyleganiu do ścian klatki piersiowej po stronie lewej, wym. do 21 x 14 mm, SUVmax do 5,5; - okołoprzełykowej - pojedynczy (Im fuz 112), śr. do 8 mm wg PET, SUVmax do 5,8. Aktywne metabolicznie węzły chłonne pachowe - po stronie prawej największy wym. do 25 x 12 mm, SUVmax do 5,5; po lewej pojedynczy aktywny, śr. do 11 mm, SUVmax 6,4.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W miąższu płuca lewego przyśródpiersiowo nieliczne, nieco nieregularne nieliczne obszary litej konsolidacji miąższu wym. do 10 x 5 mm (Im TK 350)  Obszar nieaktywnej metabolicznie litej konsolidacji miąższu płucnego w segm. III lewym przynaczyniowo i przysercowo, śr. do 7 mm - niecharakterystyczny do kontroli.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny pobudzony metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy, SUVmax do 3,9. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Wartości referencyjne: MBPS SUVmax 1,4. Prawy płat wątroby SUVmax do 2,1.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego po jednej stronie przepony. Poza tym zgodnie z opisem.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>12.3</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>13.06.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>HL, ocena po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 93mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej okolicy szyi i karku, SUV max do 11,9, w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 11mm. Aktywność metaboliczna w topografii  migdałka gardłowego, SUVmax do 7,1 - do ew. oceny laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej klatki piersiowej i śródpiersia, SUV max do 7,8, w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 10mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 32x21mm - lewobocznie (Im CT 295), w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 305) - masy resztkowe do dalszej kontroli.   Brzuch i miednica: Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej pomiędzy nerką lewą a śledzioną, SUV max do 5,6.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Wartości referencyjne: MBPS SUVmax 1,2, Prawy płat wątroby SUVmax do 2,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym zgodnie z opisem.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>11.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>07.09.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>HL, ocena po 4 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 59min od podania 18F-FDG. Glikemia: 101mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej okolicy szyi i karku, SUV max do 11,9 - wzmożone cieniowania tkanki tłuszczowej, nie da się wykluczyć drobnych do 10mm węzłów chłonnych wśród zwiekszonego metabolizmu tkanki tłuszczowej- do kontroli.  Zwiększona aktywność metaboliczna w topografii  migdałka gardłowego, SUVmax 5,9 - do ew. oceny laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej klatki piersiowej i śródpiersia w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 8mm.  Aktywne metabolicznie węzły chłonne przy łuku aorty wielkości do 19mm wg PET, SUV max do 9,6.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 42x23mm - lewobocznie (Im CT 304) - jak poprzednio, w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 306) - masy resztkowe do dalszej kontroli.  Brzuch i miednica: Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej jamy brzusznej i miednicy. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Wartości referencyjne: MBPS SUVmax 1,6 Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych przy łuku aorty. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>11.9</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>12.01.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>HL, ocena po II linii leczenia.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 42x23mm - lewobocznie (Im CT 304) - jak poprzednio, w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 306) - masy resztkowe do dalszej kontroli. Węzły chłonne separujące się przy naczyniach podobojczykowych lewych wielkości do 19mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej - nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej.   Wartości referencyjne: MBPS SUVmax 1,6 Prawy płat wątroby SUVmax do 2,3.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2.3</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>01.08.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina NSCHL. Ocena kontrolna: +100 doba po autoSCT.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 56 min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych. Drobne przyścienne zgrubienie błony śluzowej w zacyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy resztkowe w śródpiersiu przednim, pośrodkowo i po stronie lewej wielkości ok. 47x20mm. Separujące się masy miękkotkankowe w śródpiersiu po stronie lewej wielkości do 22x17mm. Dokładna ocena mas reztkowych możliwa w badaniu TK KLP z kontrastem dożylnym. Węzły chłonne nad- i podobojczykowe lewe wielkości do 15x10mm. Drobny obszar zagęszczeń miąższowych obwodowo w segm. 10 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Wzmożony metabolizm FDG nadwpustowo w przełyku SUV max 6,3- odczynowo? Wzmożony metabolizm FDG w jelitach położonych w miednicy SUV max do 7,8- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Krawędź przednia dolna trzonu L1 zniekształcona, o nierównym obrysie, z widocznym zwapnieniem w więzadle podłużnym przednim lub drobnym odłamem kostnym/odszczepionym jądrem kostnienia w przyleganiu. Nierówne obrysy blaszek granicznych trzonów kręgowych oraz drobne i miernie wydatne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych, zwłaszcza w środkowym i dolnym odcinku kręgosłupa piersiowego. Os sacrum arcuatum. Ok. 7mm wyspa kostna w głowie prawej kości ramiennej oraz drobna w lewej.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej.  Wartości referencyjne: MBPS SUVmax 1,5; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Masy miękkotkankowe w śródpiersiu - do dalszej kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>7.8</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>04.06.2024</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina NSCHL. Ocena odpowiedzi po leczeniu.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 89mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetrycznie wzmożona aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max 13,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych. Niewielkie przyścienne zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Częściowo rozfragmentowane masy resztkowe w śródpiersiu przednim pośrodkowo wielkości do ok. 35x20mm. Separujące się masy miękkotkankowe w śródpiersiu po stronie lewej wielkości do 22x17mm. Dokładna ocena mas resztkowych możliwa w badaniu TK KLP z kontrastem dożylnym. Węzły chłonne nad- i podobojczykowe lewe wielkości do 15x10mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Wzmożony metabolizm FDG nadwpustowo w przełyku SUV max 6,3- odczynowo? Wzmożony metabolizm FDG w jelitach położonych w miednicy, głownie po stronie prawej SUV max do 10,3 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Krawędź przednia dolna trzonu L1 zniekształcona, o nierównym obrysie, z widocznym zwapnieniem w więzadle podłużnym przednim lub drobnym odłamem kostnym/odszczepionym jądrem kostnienia w przyleganiu. Nierówne obrysy blaszek granicznych trzonów kręgowych oraz drobne i miernie wydatne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych, zwłaszcza w środkowym i dolnym odcinku kręgosłupa piersiowego. Os sacrum arcuatum. Ok. 7mm wyspa kostna w głowie prawej kości ramiennej oraz drobna w lewej.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej, pośród której widoczne są pojedyncze drobne węzły chłonne.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Masy miękkotkankowe w śródpiersiu - do dalszej kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>13.1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MATEUSZ JANIK.xlsx
+++ b/pacjenci/MATEUSZ JANIK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 58 min od podania 18F-FDG. Glikemia: 117mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie liczne powiększone węzły chłonne szyjne : - przestrzeni przygardłowej obustronnie - po prawej śr. do 16 mm, spakietowane, SUVmax do 8,7, po lewej wym. do 14 x 20 mm, SUVmax do 10,4; - grup Ib - po prawej pojedyncze, graniczne, wym. do 11 x 8 mm, SUVmax 3,6; po lewej kilka częściowo spakietowanych wym. do 15 x 23 mm, SUVmax do 9,9; - grup II - po prawej mniej liczne, częściowo spakietowane w tym z grupą V po tej stronie, na przekrojach poprzecznych wym. do 26 x 16 mm (wg PET), SUVmax do 9,4; po lewej liczniejsze, spakietowane w ciągłości z grupą V po tej stronie, wym. do 37 x 48 mm, SUVmax do 10,6; - grup III-IV - po prawej liczniejsze, spakietowane, w ciągłości z pakietami węzłów nad- i podobojczykowych po tej stronie; największe pakiety na przekroju poprzecznym wym. do 36 x 30 mm, SUVmax do 11,4; po lewej mniej liczne, częściowo spakietowane, w ciągłości z pakietami nadobojczykowymi po tej stronie, wym. do 24 x 36 mm, SUVmax do 6,6;  - grup V - po prawej bardzo liczne spakietowane ciągnące się przez całą grupę, w największym wymiarze na przekroju poprzecznym ok. 39 x 50 mm, SUVmax do 12,3; po lewej nieco mniej liczne, częściowo spakietowane - największe wym. do 24 x 20 mm, SUVmax do 7,2. Aktywność metaboliczna w strukturach pierścienia chłonnego gardła, szczególnie wydatna w obrębie migdałków podniebiennych - obustronnie w przeglądowym TK wydają się być powiększone wym. do 15,9 mm (wg PET), SUVmax do 4,0.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyczne i spakietowane w grupach: - nad- i podobojczykowych oraz śródpiersia górnego w tym przymostkowe  po prawej w łączności z grupą IV szyjną, wym. do 40 x 19 mm, SUVmax do 7,1;  - nad- i podobojczykowych oraz śródpiersia górnego w tym przymostkowe po lewej w łączności z grupami węzłów przynaczyniowych i okna aortalno-płucnego, największy pakiet wym. do 56 x 38 mm, SUVmax do 10,8; - przytchawiczych górnych oraz dolnych - po prawej wielkości do 34 x 22 mm, SUVmax do 8,6; po lewej nieliczne wym. do 17 x 10 mm, SUVmax do 4,0; - podostrogowej i wnękowej po stronie prawej - wym. do 27 x 20 mm, SUVmax do 7,3; - wnękowej i oskrzelowo-płucnej po stronie lewej -  wym. do 23 x 17 mm wg PET, SUVmax do 11,2; - przedsercowej - w zachyłku przeponowo-sercowym tuż nad przeponą, poniżej koniuszka serca i w przyleganiu do ścian klatki piersiowej po stronie lewej, wym. do 21 x 14 mm, SUVmax do 5,5; - okołoprzełykowej - pojedynczy (Im fuz 112), śr. do 8 mm wg PET, SUVmax do 5,8. Aktywne metabolicznie węzły chłonne pachowe - po stronie prawej największy wym. do 25 x 12 mm, SUVmax do 5,5; po lewej pojedynczy aktywny, śr. do 11 mm, SUVmax 6,4.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W miąższu płuca lewego przyśródpiersiowo nieliczne, nieco nieregularne nieliczne obszary litej konsolidacji miąższu wym. do 10 x 5 mm (Im TK 350)  Obszar nieaktywnej metabolicznie litej konsolidacji miąższu płucnego w segm. III lewym przynaczyniowo i przysercowo, śr. do 7 mm - niecharakterystyczny do kontroli.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny pobudzony metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy, SUVmax do 3,9. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Wartości referencyjne: MBPS SUVmax 1,4. Prawy płat wątroby SUVmax do 2,1.</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie liczne powiększone węzły chłonne szyjne : - przestrzeni przygardłowej obustronnie - po prawej śr. do 16 mm, spakietowane, SUVmax do 8,7, po lewej wym. do 14 x 20 mm, SUVmax do 10,4; - grup Ib - po prawej pojedyncze, graniczne, wym. do 11 x 8 mm, SUVmax 3,6; po lewej kilka częściowo spakietowanych wym. do 15 x 23 mm, SUVmax do 9,9; - grup II - po prawej mniej liczne, częściowo spakietowane w tym z grupą V po tej stronie, na przekrojach poprzecznych wym. do 26 x 16 mm (wg PET), SUVmax do 9,4; po lewej liczniejsze, spakietowane w ciągłości z grupą V po tej stronie, wym. do 37 x 48 mm, SUVmax do 10,6; - grup III-IV - po prawej liczniejsze, spakietowane, w ciągłości z pakietami węzłów nad- i podobojczykowych po tej stronie; największe pakiety na przekroju poprzecznym wym. do 36 x 30 mm, SUVmax do 11,4; po lewej mniej liczne, częściowo spakietowane, w ciągłości z pakietami nadobojczykowymi po tej stronie, wym. do 24 x 36 mm, SUVmax do 6,6;  - grup V - po prawej bardzo liczne spakietowane ciągnące się przez całą grupę, w największym wymiarze na przekroju poprzecznym ok. 39 x 50 mm, SUVmax do 12,3; po lewej nieco mniej liczne, częściowo spakietowane - największe wym. do 24 x 20 mm, SUVmax do 7,2. Aktywność metaboliczna w strukturach pierścienia chłonnego gardła, szczególnie wydatna w obrębie migdałków podniebiennych - obustronnie w przeglądowym TK wydają się być powiększone wym. do 15,9 mm (wg PET), SUVmax do 4,0.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pojedyczne i spakietowane w grupach: - nad- i podobojczykowych oraz śródpiersia górnego w tym przymostkowe  po prawej w łączności z grupą IV szyjną, wym. do 40 x 19 mm, SUVmax do 7,1;  - nad- i podobojczykowych oraz śródpiersia górnego w tym przymostkowe po lewej w łączności z grupami węzłów przynaczyniowych i okna aortalno-płucnego, największy pakiet wym. do 56 x 38 mm, SUVmax do 10,8; - przytchawiczych górnych oraz dolnych - po prawej wielkości do 34 x 22 mm, SUVmax do 8,6; po lewej nieliczne wym. do 17 x 10 mm, SUVmax do 4,0; - podostrogowej i wnękowej po stronie prawej - wym. do 27 x 20 mm, SUVmax do 7,3; - wnękowej i oskrzelowo-płucnej po stronie lewej -  wym. do 23 x 17 mm wg PET, SUVmax do 11,2; - przedsercowej - w zachyłku przeponowo-sercowym tuż nad przeponą, poniżej koniuszka serca i w przyleganiu do ścian klatki piersiowej po stronie lewej, wym. do 21 x 14 mm, SUVmax do 5,5; - okołoprzełykowej - pojedynczy (Im fuz 112), śr. do 8 mm wg PET, SUVmax do 5,8. Aktywne metabolicznie węzły chłonne pachowe - po stronie prawej największy wym. do 25 x 12 mm, SUVmax do 5,5; po lewej pojedynczy aktywny, śr. do 11 mm, SUVmax 6,4.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W miąższu płuca lewego przyśródpiersiowo nieliczne, nieco nieregularne nieliczne obszary litej konsolidacji miąższu wym. do 10 x 5 mm (Im TK 350)  Obszar nieaktywnej metabolicznie litej konsolidacji miąższu płucnego w segm. III lewym przynaczyniowo i przysercowo, śr. do 7 mm - niecharakterystyczny do kontroli.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny pobudzony metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy, SUVmax do 3,9. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego po jednej stronie przepony. Poza tym zgodnie z opisem.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>12.3</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 93mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej okolicy szyi i karku, SUV max do 11,9, w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 11mm. Aktywność metaboliczna w topografii  migdałka gardłowego, SUVmax do 7,1 - do ew. oceny laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej klatki piersiowej i śródpiersia, SUV max do 7,8, w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 10mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 32x21mm - lewobocznie (Im CT 295), w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 305) - masy resztkowe do dalszej kontroli.   Brzuch i miednica: Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej pomiędzy nerką lewą a śledzioną, SUV max do 5,6.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Wartości referencyjne: MBPS SUVmax 1,2, Prawy płat wątroby SUVmax do 2,0.</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej okolicy szyi i karku, SUV max do 11,9, w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 11mm. Aktywność metaboliczna w topografii  migdałka gardłowego, SUVmax do 7,1 - do ew. oceny laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej klatki piersiowej i śródpiersia, SUV max do 7,8, w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 10mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 32x21mm - lewobocznie (Im CT 295), w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 305) - masy resztkowe do dalszej kontroli.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej pomiędzy nerką lewą a śledzioną, SUV max do 5,6.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym zgodnie z opisem.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>11.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 59min od podania 18F-FDG. Glikemia: 101mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej okolicy szyi i karku, SUV max do 11,9 - wzmożone cieniowania tkanki tłuszczowej, nie da się wykluczyć drobnych do 10mm węzłów chłonnych wśród zwiekszonego metabolizmu tkanki tłuszczowej- do kontroli.  Zwiększona aktywność metaboliczna w topografii  migdałka gardłowego, SUVmax 5,9 - do ew. oceny laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej klatki piersiowej i śródpiersia w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 8mm.  Aktywne metabolicznie węzły chłonne przy łuku aorty wielkości do 19mm wg PET, SUV max do 9,6.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 42x23mm - lewobocznie (Im CT 304) - jak poprzednio, w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 306) - masy resztkowe do dalszej kontroli.  Brzuch i miednica: Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej jamy brzusznej i miednicy. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Wartości referencyjne: MBPS SUVmax 1,6 Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej okolicy szyi i karku, SUV max do 11,9 - wzmożone cieniowania tkanki tłuszczowej, nie da się wykluczyć drobnych do 10mm węzłów chłonnych wśród zwiekszonego metabolizmu tkanki tłuszczowej- do kontroli.  Zwiększona aktywność metaboliczna w topografii  migdałka gardłowego, SUVmax 5,9 - do ew. oceny laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej klatki piersiowej i śródpiersia w jej topografii widoczne są obszary o wzmożonej densyjności oraz drobne węzły chłonne średnicy do 8mm.  Aktywne metabolicznie węzły chłonne przy łuku aorty wielkości do 19mm wg PET, SUV max do 9,6.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 42x23mm - lewobocznie (Im CT 304) - jak poprzednio, w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 306) - masy resztkowe do dalszej kontroli.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zwiększona aktywność metaboliczna w obrębie brunatnej tkanki tłuszczowej jamy brzusznej i miednicy. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych przy łuku aorty. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>11.9</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 42x23mm - lewobocznie (Im CT 304) - jak poprzednio, w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 306) - masy resztkowe do dalszej kontroli. Węzły chłonne separujące się przy naczyniach podobojczykowych lewych wielkości do 19mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej - nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej.   Wartości referencyjne: MBPS SUVmax 1,6 Prawy płat wątroby SUVmax do 2,3.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Pojedyncze drobne zmiany śluzówkowe zatoki szczękowej prawej. Hipoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim widoczne są masy miękkotkankowe o wymiarach około 42x23mm - lewobocznie (Im CT 304) - jak poprzednio, w śródpiersiu przednim na długości około 76mm, grubości do 18mm (Im CT 306) - masy resztkowe do dalszej kontroli. Węzły chłonne separujące się przy naczyniach podobojczykowych lewych wielkości do 19mm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Krawędzi przednia dolna L1 zniekształcona, o nierównym obrysie z widocznym zwapnieniem w więzadle podłużnym przednim - być może zmiany pozapalne. Nieliczne guzki Schmorla blaszek granicznych dolnego odcinka kręgosłupa piersiowego.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej - nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 56 min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych. Drobne przyścienne zgrubienie błony śluzowej w zacyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy resztkowe w śródpiersiu przednim, pośrodkowo i po stronie lewej wielkości ok. 47x20mm. Separujące się masy miękkotkankowe w śródpiersiu po stronie lewej wielkości do 22x17mm. Dokładna ocena mas reztkowych możliwa w badaniu TK KLP z kontrastem dożylnym. Węzły chłonne nad- i podobojczykowe lewe wielkości do 15x10mm. Drobny obszar zagęszczeń miąższowych obwodowo w segm. 10 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Wzmożony metabolizm FDG nadwpustowo w przełyku SUV max 6,3- odczynowo? Wzmożony metabolizm FDG w jelitach położonych w miednicy SUV max do 7,8- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Krawędź przednia dolna trzonu L1 zniekształcona, o nierównym obrysie, z widocznym zwapnieniem w więzadle podłużnym przednim lub drobnym odłamem kostnym/odszczepionym jądrem kostnienia w przyleganiu. Nierówne obrysy blaszek granicznych trzonów kręgowych oraz drobne i miernie wydatne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych, zwłaszcza w środkowym i dolnym odcinku kręgosłupa piersiowego. Os sacrum arcuatum. Ok. 7mm wyspa kostna w głowie prawej kości ramiennej oraz drobna w lewej.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej.  Wartości referencyjne: MBPS SUVmax 1,5; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych. Drobne przyścienne zgrubienie błony śluzowej w zacyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy resztkowe w śródpiersiu przednim, pośrodkowo i po stronie lewej wielkości ok. 47x20mm. Separujące się masy miękkotkankowe w śródpiersiu po stronie lewej wielkości do 22x17mm. Dokładna ocena mas reztkowych możliwa w badaniu TK KLP z kontrastem dożylnym. Węzły chłonne nad- i podobojczykowe lewe wielkości do 15x10mm. Drobny obszar zagęszczeń miąższowych obwodowo w segm. 10 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG nadwpustowo w przełyku SUV max 6,3- odczynowo? Wzmożony metabolizm FDG w jelitach położonych w miednicy SUV max do 7,8- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Krawędź przednia dolna trzonu L1 zniekształcona, o nierównym obrysie, z widocznym zwapnieniem w więzadle podłużnym przednim lub drobnym odłamem kostnym/odszczepionym jądrem kostnienia w przyleganiu. Nierówne obrysy blaszek granicznych trzonów kręgowych oraz drobne i miernie wydatne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych, zwłaszcza w środkowym i dolnym odcinku kręgosłupa piersiowego. Os sacrum arcuatum. Ok. 7mm wyspa kostna w głowie prawej kości ramiennej oraz drobna w lewej.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Masy miękkotkankowe w śródpiersiu - do dalszej kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>7.8</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 89mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożona aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max 13,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych. Niewielkie przyścienne zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Częściowo rozfragmentowane masy resztkowe w śródpiersiu przednim pośrodkowo wielkości do ok. 35x20mm. Separujące się masy miękkotkankowe w śródpiersiu po stronie lewej wielkości do 22x17mm. Dokładna ocena mas resztkowych możliwa w badaniu TK KLP z kontrastem dożylnym. Węzły chłonne nad- i podobojczykowe lewe wielkości do 15x10mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Wzmożony metabolizm FDG nadwpustowo w przełyku SUV max 6,3- odczynowo? Wzmożony metabolizm FDG w jelitach położonych w miednicy, głownie po stronie prawej SUV max do 10,3 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Krawędź przednia dolna trzonu L1 zniekształcona, o nierównym obrysie, z widocznym zwapnieniem w więzadle podłużnym przednim lub drobnym odłamem kostnym/odszczepionym jądrem kostnienia w przyleganiu. Nierówne obrysy blaszek granicznych trzonów kręgowych oraz drobne i miernie wydatne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych, zwłaszcza w środkowym i dolnym odcinku kręgosłupa piersiowego. Os sacrum arcuatum. Ok. 7mm wyspa kostna w głowie prawej kości ramiennej oraz drobna w lewej.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej, pośród której widoczne są pojedyncze drobne węzły chłonne.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożona aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max 13,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych. Niewielkie przyścienne zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Częściowo rozfragmentowane masy resztkowe w śródpiersiu przednim pośrodkowo wielkości do ok. 35x20mm. Separujące się masy miękkotkankowe w śródpiersiu po stronie lewej wielkości do 22x17mm. Dokładna ocena mas resztkowych możliwa w badaniu TK KLP z kontrastem dożylnym. Węzły chłonne nad- i podobojczykowe lewe wielkości do 15x10mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG nadwpustowo w przełyku SUV max 6,3- odczynowo? Wzmożony metabolizm FDG w jelitach położonych w miednicy, głownie po stronie prawej SUV max do 10,3 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie struktur kręgosłupa i kości miednicy. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Krawędź przednia dolna trzonu L1 zniekształcona, o nierównym obrysie, z widocznym zwapnieniem w więzadle podłużnym przednim lub drobnym odłamem kostnym/odszczepionym jądrem kostnienia w przyleganiu. Nierówne obrysy blaszek granicznych trzonów kręgowych oraz drobne i miernie wydatne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych, zwłaszcza w środkowym i dolnym odcinku kręgosłupa piersiowego. Os sacrum arcuatum. Ok. 7mm wyspa kostna w głowie prawej kości ramiennej oraz drobna w lewej.  Inne: Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi, KLP i jamy brzusznej, pośród której widoczne są pojedyncze drobne węzły chłonne.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Masy miękkotkankowe w śródpiersiu - do dalszej kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>13.1</v>
       </c>
     </row>
